--- a/Evaluate/danhgia2Economy.xlsx
+++ b/Evaluate/danhgia2Economy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>ROUGE-2 Recall</t>
   </si>
@@ -45,19 +45,16 @@
 + energy-based-distance(1 cluster winner) trước khi đưa vào llm trả lời sẽ có bước đưa cluster winner vào llm để đánh giá từng đoạn context có liên quan không, sau đó sẽ đưa tài liệu có liên quan vào llm để sinh câu trả lời) 
 + gpt-5-mini</t>
   </si>
-  <si>
-    <t xml:space="preserve">Đã xem và chỉnh sửa lại điểm Hit@5 và Mean Reciprocal Rank </t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -75,14 +72,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -90,14 +79,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -106,9 +87,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -122,15 +102,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -141,51 +115,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -198,14 +127,46 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,6 +179,42 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -240,175 +237,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,17 +451,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -482,16 +468,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -513,174 +499,185 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1013,8 +1010,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="12.75" outlineLevelRow="3"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="12.75" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="37.1" customWidth="1"/>
     <col min="2" max="2" width="14.8" customWidth="1"/>
@@ -1081,11 +1078,6 @@
         <v>0.834714898</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
